--- a/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>NU</t>
   </si>
@@ -656,205 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2474300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1980800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2067400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1919500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1626300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1377900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1436900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1408100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1423700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1244500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1206800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>971600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>824800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>709400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1450500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1306900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1157600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>877300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>636000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>480900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>336100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>245100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>202600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>156100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>162300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -897,124 +904,130 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>457000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>504400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>455500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>307500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>209400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>130000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>87000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>58100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>70600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>55900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>47900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2474300</v>
+      </c>
+      <c r="E10" s="3">
         <v>1980800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2067400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1919500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1626300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1377900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1436900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1408100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1423700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1244500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1206800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>971600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>824800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>709400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>993500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>802500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>702100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>569800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>426600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>350900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>249100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>187000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>132000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>100200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>114400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>149800</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1247,8 +1267,8 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1283,88 +1303,94 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E15" s="3">
         <v>11800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>71000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>47900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>15600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>18500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>14000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>9900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>10400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>7700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>6400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>5700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1233400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1025400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>989400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>802100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>745900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>581700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>669500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>684300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>698300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>665900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>646900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>560100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>465800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1672300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1301800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1182200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>944900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>724500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>502700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>342600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>298400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>228400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>180700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>157400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1241000</v>
+      </c>
+      <c r="E18" s="3">
         <v>955300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1078100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1117500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>880400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>796200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>767500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>723800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>725400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>578500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>559900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>411500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>324000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>243600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-221800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-24600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-67600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-88500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-21800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-53300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-25800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-24600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,29 +1613,30 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1624,8 +1658,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1649,99 +1683,105 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-88000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-13200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1260300</v>
+      </c>
+      <c r="E21" s="3">
         <v>966100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1148700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1126800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>886700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>804200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>815300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>739400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>730000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>597000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>576500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>430700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>338000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>256800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-211900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-14200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-60000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-82100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-16100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-50900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-110100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1784,8 +1824,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1820,168 +1860,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1236300</v>
+      </c>
+      <c r="E23" s="3">
         <v>954300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1077700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1116300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>879400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>795100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>767500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>723800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>725400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>578500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>559900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>411500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>324000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>243600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-221700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-24600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-67700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-88500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-21800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-53400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-113800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-37800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-46500</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>175200</v>
+      </c>
+      <c r="E24" s="3">
         <v>82900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>182900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>333600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>242400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>237900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>214800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>170400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>238100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>199700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>199100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>108500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>99100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>101900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>75900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-22600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-22200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>12600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1061100</v>
+      </c>
+      <c r="E26" s="3">
         <v>871400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>894800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>782700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>637000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>557200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>552600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>553400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>487300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>378800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>360900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>303000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>224900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>141800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-297600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-29900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-45000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-66300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-34400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-15200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-107100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-32600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1060200</v>
+      </c>
+      <c r="E27" s="3">
         <v>872100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>892400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>782500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>636800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>557200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>552600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>553400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>487300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>378800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>360900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>303000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>224900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>141800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-297600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-29700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-45100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-66100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-34200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-15200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-107100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-32600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,29 +2607,32 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
@@ -2584,8 +2654,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2609,99 +2679,105 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>88000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>13200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1060200</v>
+      </c>
+      <c r="E33" s="3">
         <v>872100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>892400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>782500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>636800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>557200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>552600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>553400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>487300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>378800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>360900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>303000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>224900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>141800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-297600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-29700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-45100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-66100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-34200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-15200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-107100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-32600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1060200</v>
+      </c>
+      <c r="E35" s="3">
         <v>872100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>892400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>782500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>636800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>557200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>552600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>553400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>487300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>378800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>360900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>303000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>224900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>141800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-297600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-29700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-45100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-66100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-34200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-15200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-107100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-32600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,77 +3091,78 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10455200</v>
+      </c>
+      <c r="E41" s="3">
         <v>10173100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11392100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9153200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8943700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7554000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6893900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5515100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6943200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6033600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5923400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3208900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5743600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4310500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3959100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1803600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1079100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>905300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>177000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>167600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>185100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>252600</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3085,53 +3172,56 @@
       <c r="AB41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4715600</v>
+      </c>
+      <c r="E42" s="3">
         <v>5733600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4939900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5529900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5179300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3479000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3336500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2742500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2697600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1021400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>635800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>374600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>825900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>108700</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3165,70 +3255,73 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>940800</v>
+      </c>
+      <c r="E43" s="3">
         <v>844200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>748800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>756900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>701200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>651500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>254800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>170000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>22100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>428700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>352200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>253800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12436700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>521700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>381800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>374200</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -3245,8 +3338,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3289,8 +3385,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3325,77 +3421,80 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E45" s="3">
         <v>95700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>119200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>108300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>96000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>63400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>85900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>90700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>81500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>66500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>100200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>140500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>133000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3032400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>61700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>44900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>59900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>51900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>16000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>16300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3405,53 +3504,56 @@
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25578100</v>
+      </c>
+      <c r="E46" s="3">
         <v>26138000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>26830600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23806600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23227400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19209200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17345600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15427800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16538900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14301700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14617300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10010000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9857200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>19888400</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3485,77 +3587,80 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17526900</v>
+      </c>
+      <c r="E47" s="3">
         <v>13752500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15061100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13277100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11544800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10205900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10271500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11035300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8170800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8398100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8642300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8339800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5530000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7758400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>23683700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>22249600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>22212800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>21798200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>18536400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13727100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12859000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9512800</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3565,77 +3670,80 @@
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E48" s="3">
         <v>75200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>49800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>46100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>46200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>53500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>56200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>65500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>69800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>62000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>51700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>46500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>37900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>40500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>37200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>17900</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3645,77 +3753,80 @@
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1156500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1109600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1011000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>985300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>924600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>848700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>761900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>798400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>703600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>705000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>693400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>675400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>651900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>612800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>579600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>565300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>557000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>530100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>474200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>455700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>450900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>13000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,77 +4002,80 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>710600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1081400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>411200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>951000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>689900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>534400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>474300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>558400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>406400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>347100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>248400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>260700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1926300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>48300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>968500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>820000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>710200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>676100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>436900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>392500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>321500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>215000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,77 +4168,80 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>82753400</v>
+      </c>
+      <c r="E54" s="3">
         <v>77456400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>74893900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>68362800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>62730100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>54192500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>49931200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>48637900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44802700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43839500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>43345200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35693200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33608100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29489400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29934900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26007000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25188700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>24258000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>19858700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14926100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13951500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10121100</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,77 +4315,78 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45328400</v>
+      </c>
+      <c r="E57" s="3">
         <v>42448100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>41925100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>38775900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36640200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31564400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28855100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28319100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>25228600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24254900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>23691100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19117200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18033700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15757700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7054800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5894400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5931000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5920800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4882200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4127700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3990400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2982500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4265,77 +4396,80 @@
       <c r="AB57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3973300</v>
+      </c>
+      <c r="E58" s="3">
         <v>4283100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3375200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3527800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2436300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1362900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>755200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>841500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>888500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>754300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>352200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>297100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>229300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>191500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>16044100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14131600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>13310100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>12600100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>9670300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8089800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7505700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5497200</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4345,77 +4479,80 @@
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16528500</v>
+      </c>
+      <c r="E59" s="3">
         <v>14756200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15001400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9495700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8554800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>487300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10396500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9604700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9504600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9915300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10994700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8713900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8337600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7151000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>601600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>430900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>308000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>256400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>339100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>234800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>160800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>75900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4425,53 +4562,56 @@
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>66262000</v>
+      </c>
+      <c r="E60" s="3">
         <v>61933700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>60651900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>52128400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47957700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33613900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40272200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38987900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35832600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35131700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35303200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28298500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26763600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>23201400</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4505,77 +4645,80 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1923400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1864300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1902000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1251500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1055800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>956300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1342300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1311700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1518100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1345100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1063700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1035600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>744800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>636500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>567600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>441400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>495900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>168000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>164900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>169900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>117100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>513600</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4585,77 +4728,80 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1232200</v>
+      </c>
+      <c r="E62" s="3">
         <v>982800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>941000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4319300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4034200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10928000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>598000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>622500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>465800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>492400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>503500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>333400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>315200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>348000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>59100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>59600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>60600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>64600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>47400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>97700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>69800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>53700</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,77 +5060,80 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69501700</v>
+      </c>
+      <c r="E66" s="3">
         <v>64864600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63572300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57809300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53154000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45583600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>42284100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40993500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37879300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37036800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36938800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29803900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27963500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24280900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25044100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21254300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20450500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19469000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15417600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13022400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12014400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9317200</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,77 +5506,80 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7083700</v>
+      </c>
+      <c r="E72" s="3">
         <v>6023700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5151400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4259100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3476600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2839700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2280300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1748900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1195600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>708300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>329500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-31400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-334400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-559300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>64600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-45900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-95900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-116800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-128400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-108900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-104800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-117300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,77 +5838,80 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13249700</v>
+      </c>
+      <c r="E76" s="3">
         <v>12588800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11290900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10552000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9574800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8607900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7646300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7644300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6923400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6802700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6406400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5889300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5644600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5208500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4890800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4752700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4738200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4789000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4441000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1903700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1937100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>803800</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1060200</v>
+      </c>
+      <c r="E81" s="3">
         <v>872100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>892400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>782500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>636800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>557200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>552600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>553400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>487300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>378800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>360900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>303000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>224900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>141800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-297600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-29700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-45100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-66100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-34200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-15200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-107100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-32600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,88 +6208,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E83" s="3">
         <v>4700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>19200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>6400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2921300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1729400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2682700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2971300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2149100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1557800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>267800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4186000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1548200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1141500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1631900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4460300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-450400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>94300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>228400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>464300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>78300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1859100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-796200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-47100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-221900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-191600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>564800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>660700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +6820,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5400</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-33600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-38300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-14700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-75200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-64100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-125300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-71500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-81400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-247900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-42500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-30900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-47500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-52100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-46500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-33600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-27700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-38200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-30100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-109300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6994,8 +7228,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,244 +7513,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2546300</v>
+      </c>
+      <c r="E100" s="3">
         <v>435300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4797500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2741900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5138200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2473900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1423700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2805500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1580000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>829100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4348300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1553200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2218300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>19900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>105300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>324200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>225600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2541200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>61400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>339000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>394400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-15600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>291500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E101" s="3">
         <v>263500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>96400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>538400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-618000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>449400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>24300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>148700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>70500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>173600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>41800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-28500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>173600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>41800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-28500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>57000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>78600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>279200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-310400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>505500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-388800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-74700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-143000</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-368800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1083200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2107900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-373200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2985000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1098300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1540000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-884600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2496700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>110200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2709800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2961400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1864600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>138200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>479500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>732400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>262900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>709000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-665700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>461800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-143100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>286500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>149800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>874900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-214100</v>
       </c>
     </row>
